--- a/simulations/AON_100/economics_AON_100.xlsx
+++ b/simulations/AON_100/economics_AON_100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\AON_100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF284E3-EC4E-4869-9328-0EF3A484A974}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131E237E-A069-4370-8587-51830D9528CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -852,6 +852,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -873,7 +874,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1349,16 +1349,16 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="48" t="s">
+      <c r="A13" s="49" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="50"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="51"/>
       <c r="J13" s="33" t="s">
         <v>46</v>
       </c>
@@ -1502,16 +1502,16 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="50"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="51"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="D17" s="21">
         <f>I17/J17</f>
-        <v>298.77983839255648</v>
+        <v>419.54921642527501</v>
       </c>
       <c r="E17" s="8">
         <v>28000</v>
@@ -1538,13 +1538,13 @@
       </c>
       <c r="H17" s="9">
         <f>(E17+(F17*(D17^G17)))/1000000*J17</f>
-        <v>0.15688934468014293</v>
+        <v>0.83048944072608999</v>
       </c>
       <c r="I17" s="46">
-        <v>597.55967678511297</v>
+        <v>3356.3937314022</v>
       </c>
       <c r="J17" s="47">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="D18" s="21">
         <f>I18/J18</f>
-        <v>499.27777342721697</v>
+        <v>298.77983839278198</v>
       </c>
       <c r="E18" s="8">
         <v>28000</v>
@@ -1572,13 +1572,13 @@
       </c>
       <c r="H18" s="9">
         <f>(E18+(F18*(D18^G18)))/1000000*J18</f>
-        <v>1.5783609451117344</v>
+        <v>0.15688934468023433</v>
       </c>
       <c r="I18" s="46">
-        <v>6490.6110545538204</v>
+        <v>597.55967678556397</v>
       </c>
       <c r="J18" s="47">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D19" s="21">
         <f>I19/J19</f>
-        <v>419.54921642522874</v>
+        <v>286.42402459129897</v>
       </c>
       <c r="E19" s="8">
         <v>28000</v>
@@ -1606,13 +1606,13 @@
       </c>
       <c r="H19" s="9">
         <f>(E19+(F19*(D19^G19)))/1000000*J19</f>
-        <v>0.83048944072600983</v>
+        <v>7.5951819537075499E-2</v>
       </c>
       <c r="I19" s="46">
-        <v>3356.3937314018299</v>
+        <v>286.42402459129897</v>
       </c>
       <c r="J19" s="47">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" s="21">
         <f>I20/J20</f>
-        <v>286.42402382965702</v>
+        <v>499.27777342721697</v>
       </c>
       <c r="E20" s="8">
         <v>28000</v>
@@ -1640,26 +1640,26 @@
       </c>
       <c r="H20" s="9">
         <f>(E20+(F20*(D20^G20)))/1000000*J20</f>
-        <v>7.5951819384062716E-2</v>
+        <v>1.5783609451117344</v>
       </c>
       <c r="I20" s="46">
-        <v>286.42402382965702</v>
+        <v>6490.6110545538204</v>
       </c>
       <c r="J20" s="47">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="51" t="s">
+      <c r="A21" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="53"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="54"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
@@ -1690,16 +1690,16 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="48" t="s">
+      <c r="A23" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="50"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="51"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -1760,7 +1760,7 @@
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H26" s="38">
         <f>SUM(H14:H25)</f>
-        <v>6.4184044248319756</v>
+        <v>6.4184044249851606</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B30" s="21">
         <f>H26*B28/B27</f>
-        <v>7.3169087785427385</v>
+        <v>7.3169087787173677</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B31" s="21">
         <f>H26*B29/B27</f>
-        <v>9.8281441371043208</v>
+        <v>9.8281441373388834</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1823,11 +1823,11 @@
       </c>
       <c r="B34" s="40">
         <f>(B30)*((1+C3)+(C2+C5+C4+C6+C7+C8)/C9)*C9</f>
-        <v>27.365238831749846</v>
+        <v>27.365238832402962</v>
       </c>
       <c r="C34" s="40">
         <f>(B31)*((1+C3)+(C2+C5+C4+C6+C7+C8)/C9)*C9</f>
-        <v>36.757259072770168</v>
+        <v>36.757259073647433</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -1836,11 +1836,11 @@
       </c>
       <c r="B35" s="40">
         <f>0.3*B34</f>
-        <v>8.2095716495249533</v>
+        <v>8.209571649720889</v>
       </c>
       <c r="C35" s="40">
         <f>0.3*C34</f>
-        <v>11.02717772183105</v>
+        <v>11.02717772209423</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -1849,11 +1849,11 @@
       </c>
       <c r="B36" s="40">
         <f>0.3*SUM(B34:B35)</f>
-        <v>10.672443144382438</v>
+        <v>10.672443144637155</v>
       </c>
       <c r="C36" s="40">
         <f>0.3*SUM(C34:C35)</f>
-        <v>14.335331038380366</v>
+        <v>14.335331038722499</v>
       </c>
       <c r="D36"/>
     </row>
@@ -1863,11 +1863,11 @@
       </c>
       <c r="B37" s="40">
         <f>0.1*SUM(B34:B35)</f>
-        <v>3.5574810481274799</v>
+        <v>3.5574810482123853</v>
       </c>
       <c r="C37" s="40">
         <f>0.1*SUM(C34:C35)</f>
-        <v>4.7784436794601222</v>
+        <v>4.778443679574166</v>
       </c>
       <c r="D37"/>
     </row>
@@ -1877,11 +1877,11 @@
       </c>
       <c r="B38" s="40">
         <f>B34*(1+0.3)*(1+0.3+0.1)</f>
-        <v>49.804734673784729</v>
+        <v>49.804734674973396</v>
       </c>
       <c r="C38" s="40">
         <f>C34*(1+0.3)*(1+0.3+0.1)</f>
-        <v>66.898211512441719</v>
+        <v>66.898211514038337</v>
       </c>
       <c r="D38"/>
     </row>
@@ -1891,11 +1891,11 @@
       </c>
       <c r="B39" s="40">
         <f>B38*0.15</f>
-        <v>7.4707102010677087</v>
+        <v>7.4707102012460087</v>
       </c>
       <c r="C39" s="40">
         <f>C38*0.15</f>
-        <v>10.034731726866257</v>
+        <v>10.034731727105751</v>
       </c>
       <c r="D39"/>
     </row>
@@ -1905,11 +1905,11 @@
       </c>
       <c r="B40" s="40">
         <f>B38+B39</f>
-        <v>57.27544487485244</v>
+        <v>57.275444876219403</v>
       </c>
       <c r="C40" s="40">
         <f>C38+C39</f>
-        <v>76.932943239307974</v>
+        <v>76.932943241144088</v>
       </c>
       <c r="D40"/>
       <c r="O40" s="44"/>
@@ -1955,11 +1955,11 @@
       </c>
       <c r="B44" s="40">
         <f>B43*B40</f>
-        <v>7.3026174923698104</v>
+        <v>7.3026174925440976</v>
       </c>
       <c r="C44" s="40">
         <f>C43*C40</f>
-        <v>9.8089479403683377</v>
+        <v>9.808947940602442</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -1968,11 +1968,11 @@
       </c>
       <c r="B45" s="19">
         <f>B44</f>
-        <v>7.3026174923698104</v>
+        <v>7.3026174925440976</v>
       </c>
       <c r="C45" s="19">
         <f>C44</f>
-        <v>9.8089479403683377</v>
+        <v>9.808947940602442</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2032,16 +2032,16 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="54">
+      <c r="A3" s="55">
         <v>2019</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="E3" s="54">
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="E3" s="55">
         <v>2022</v>
       </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -2064,16 +2064,16 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="E5" s="54" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="E5" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
@@ -2142,30 +2142,30 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="48"/>
-      <c r="B9" s="50"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="51"/>
       <c r="C9" s="17">
         <f>SUM(C6:C8)</f>
         <v>7.3406250000000002</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="50"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="51"/>
       <c r="G9" s="17">
         <f>SUM(G6:G8)</f>
         <v>7.3406250000000002</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="E10" s="54" t="s">
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="E10" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C11" s="23">
         <f>0.03*CAPEX!B34</f>
-        <v>0.82095716495249538</v>
+        <v>0.82095716497208882</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>69</v>
@@ -2186,34 +2186,34 @@
       </c>
       <c r="G11" s="23">
         <f>0.03*CAPEX!C34</f>
-        <v>1.102717772183105</v>
+        <v>1.102717772209423</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="54"/>
-      <c r="B12" s="54"/>
+      <c r="A12" s="55"/>
+      <c r="B12" s="55"/>
       <c r="C12" s="29">
         <f>C11</f>
-        <v>0.82095716495249538</v>
-      </c>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
+        <v>0.82095716497208882</v>
+      </c>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
       <c r="G12" s="29">
         <f>G11</f>
-        <v>1.102717772183105</v>
+        <v>1.102717772209423</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="48" t="s">
+      <c r="A13" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
-      <c r="E13" s="48" t="s">
+      <c r="B13" s="50"/>
+      <c r="C13" s="51"/>
+      <c r="E13" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="49"/>
-      <c r="G13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="51"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C14" s="21">
         <f>0.65*(C6+C7+C8+C11)</f>
-        <v>5.3050284072191225</v>
+        <v>5.3050284072318581</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>72</v>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="G14" s="21">
         <f>0.65*(G6+G7+G8+G11)</f>
-        <v>5.4881728019190179</v>
+        <v>5.4881728019361251</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C15" s="21">
         <f>0.02*(CAPEX!B34+CAPEX!B35)</f>
-        <v>0.71149620962549587</v>
+        <v>0.71149620964247706</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>75</v>
@@ -2256,34 +2256,34 @@
       </c>
       <c r="G15" s="21">
         <f>0.02*(CAPEX!C34+CAPEX!C35)</f>
-        <v>0.95568873589202441</v>
+        <v>0.95568873591483328</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="54"/>
-      <c r="B16" s="54"/>
+      <c r="A16" s="55"/>
+      <c r="B16" s="55"/>
       <c r="C16" s="29">
         <f>SUM(C14:C15)</f>
-        <v>6.0165246168446185</v>
-      </c>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
+        <v>6.0165246168743352</v>
+      </c>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
       <c r="G16" s="29">
         <f>SUM(G14:G15)</f>
-        <v>6.443861537811042</v>
+        <v>6.4438615378509585</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="49"/>
-      <c r="C17" s="50"/>
-      <c r="E17" s="48" t="s">
+      <c r="B17" s="50"/>
+      <c r="C17" s="51"/>
+      <c r="E17" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="49"/>
-      <c r="G17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="51"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="C18" s="23">
         <f>0.06*CAPEX!B39</f>
-        <v>0.44824261206406252</v>
+        <v>0.44824261207476052</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>79</v>
@@ -2304,54 +2304,43 @@
       </c>
       <c r="G18" s="23">
         <f>0.06*CAPEX!C39</f>
-        <v>0.60208390361197539</v>
+        <v>0.60208390362634501</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="54"/>
-      <c r="B19" s="54"/>
+      <c r="A19" s="55"/>
+      <c r="B19" s="55"/>
       <c r="C19" s="17">
         <f>C18</f>
-        <v>0.44824261206406252</v>
-      </c>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
+        <v>0.44824261207476052</v>
+      </c>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
       <c r="G19" s="17">
         <f>G18</f>
-        <v>0.60208390361197539</v>
+        <v>0.60208390362634501</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="50"/>
+      <c r="B20" s="51"/>
       <c r="C20" s="17">
         <f>C9+C12+C16+C19</f>
-        <v>14.626349393861176</v>
-      </c>
-      <c r="E20" s="48" t="s">
+        <v>14.626349393921185</v>
+      </c>
+      <c r="E20" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="F20" s="50"/>
+      <c r="F20" s="51"/>
       <c r="G20" s="17">
         <f>G9+G12+G16+G19</f>
-        <v>15.489288213606121</v>
+        <v>15.489288213686727</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:G10"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A5:C5"/>
@@ -2361,6 +2350,17 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E19:F19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2409,15 +2409,15 @@
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
@@ -2463,8 +2463,8 @@
         <v>31</v>
       </c>
       <c r="D6" s="27">
-        <f>30690.5025430649/1000</f>
-        <v>30.690502543064902</v>
+        <f>30690.5025481741/1000</f>
+        <v>30.690502548174099</v>
       </c>
       <c r="E6" s="42">
         <v>465.07</v>
@@ -2474,19 +2474,19 @@
       </c>
       <c r="G6" s="42">
         <f>D6*E6</f>
-        <v>14273.232017703194</v>
+        <v>14273.232020079327</v>
       </c>
       <c r="H6" s="42">
         <f>D6*F6</f>
-        <v>22347.903236783568</v>
+        <v>22347.903240503932</v>
       </c>
       <c r="I6" s="11">
         <f>G6/Summary!$C$23</f>
-        <v>0.38061876855492022</v>
+        <v>0.38061876861828364</v>
       </c>
       <c r="J6" s="11">
         <f>H6/Summary!$C$23</f>
-        <v>0.59594290902151548</v>
+        <v>0.59594290912072501</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
@@ -2497,8 +2497,8 @@
         <v>31</v>
       </c>
       <c r="D7" s="27">
-        <f>30690.5025430649/1000</f>
-        <v>30.690502543064902</v>
+        <f>30690.5025481741/1000</f>
+        <v>30.690502548174099</v>
       </c>
       <c r="E7" s="42">
         <v>1313.2</v>
@@ -2508,31 +2508,31 @@
       </c>
       <c r="G7" s="42">
         <f>D7*E7</f>
-        <v>40302.767939552832</v>
+        <v>40302.767946262225</v>
       </c>
       <c r="H7" s="42">
         <f>D7*F7</f>
-        <v>41924.147188902949</v>
+        <v>41924.147195882266</v>
       </c>
       <c r="I7" s="11">
         <f>G7/Summary!$C$23</f>
-        <v>1.074738355228936</v>
+        <v>1.0747383554078527</v>
       </c>
       <c r="J7" s="11">
         <f>H7/Summary!$C$23</f>
-        <v>1.1179750497969718</v>
+        <v>1.1179750499830865</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
@@ -2542,8 +2542,8 @@
         <v>32</v>
       </c>
       <c r="D9" s="9">
-        <f>169540876.710415/1000000</f>
-        <v>169.54087671041501</v>
+        <f>169540876.715708/10^6</f>
+        <v>169.54087671570798</v>
       </c>
       <c r="E9" s="40">
         <v>0.38</v>
@@ -2554,23 +2554,23 @@
       </c>
       <c r="G9" s="42">
         <f>D9*E9</f>
-        <v>64.425533149957701</v>
+        <v>64.425533151969034</v>
       </c>
       <c r="H9" s="42">
         <f>D9*F9</f>
-        <v>86.537012428585157</v>
+        <v>86.537012431286797</v>
       </c>
       <c r="I9" s="11">
         <f>G9/Summary!$C$23</f>
-        <v>1.7180108233802135E-3</v>
+        <v>1.718010823433849E-3</v>
       </c>
       <c r="J9" s="11">
         <f>H9/Summary!$C$23</f>
-        <v>2.307649105972435E-3</v>
+        <v>2.3076491060444785E-3</v>
       </c>
       <c r="K9" s="11">
         <f>H9/Summary!$F$23</f>
-        <v>2.307649105972435E-3</v>
+        <v>2.3076491060444785E-3</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
@@ -2659,11 +2659,11 @@
       <c r="F12" s="19"/>
       <c r="G12" s="19">
         <f>(G5+G6+G9+G10+G11)/1000000*8000</f>
-        <v>115.72430573879682</v>
+        <v>115.72430575782197</v>
       </c>
       <c r="H12" s="19">
         <f>(H5+H6+H9+H10+H11)/1000000*8000</f>
-        <v>180.76205843505321</v>
+        <v>180.76205846483776</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
@@ -2678,11 +2678,11 @@
       <c r="F13" s="19"/>
       <c r="G13" s="19">
         <f>(G5+G7+G9+G10+G11)/1000000*8000</f>
-        <v>323.96059311359392</v>
+        <v>323.96059316728514</v>
       </c>
       <c r="H13" s="19">
         <f>(H5+H7+H9+H10+H11)/1000000*8000</f>
-        <v>337.37201005200831</v>
+        <v>337.37201010786441</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
@@ -2756,22 +2756,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="E2" s="54" t="s">
+      <c r="C2" s="55"/>
+      <c r="E2" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="54"/>
-      <c r="H2" s="54" t="s">
+      <c r="F2" s="55"/>
+      <c r="H2" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="I2" s="54"/>
-      <c r="K2" s="54" t="s">
+      <c r="I2" s="55"/>
+      <c r="K2" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="L2" s="54"/>
+      <c r="L2" s="55"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
@@ -2779,28 +2779,28 @@
       </c>
       <c r="C3" s="21">
         <f>SUM(CAPEX!B30)</f>
-        <v>7.3169087785427385</v>
+        <v>7.3169087787173677</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>95</v>
       </c>
       <c r="F3" s="21">
         <f>CAPEX!B31</f>
-        <v>9.8281441371043208</v>
+        <v>9.8281441373388834</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>62</v>
       </c>
       <c r="I3" s="21">
         <f t="shared" ref="I3:I18" si="0">C3</f>
-        <v>7.3169087785427385</v>
+        <v>7.3169087787173677</v>
       </c>
       <c r="K3" s="10" t="s">
         <v>95</v>
       </c>
       <c r="L3" s="21">
         <f t="shared" ref="L3:L18" si="1">F3</f>
-        <v>9.8281441371043208</v>
+        <v>9.8281441373388834</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
@@ -2809,28 +2809,28 @@
       </c>
       <c r="C4" s="21">
         <f>SUM(CAPEX!B34)</f>
-        <v>27.365238831749846</v>
+        <v>27.365238832402962</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>54</v>
       </c>
       <c r="F4" s="21">
         <f>CAPEX!C34</f>
-        <v>36.757259072770168</v>
+        <v>36.757259073647433</v>
       </c>
       <c r="H4" s="26" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="21">
         <f t="shared" si="0"/>
-        <v>27.365238831749846</v>
+        <v>27.365238832402962</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>54</v>
       </c>
       <c r="L4" s="21">
         <f t="shared" si="1"/>
-        <v>36.757259072770168</v>
+        <v>36.757259073647433</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
@@ -2839,28 +2839,28 @@
       </c>
       <c r="C5" s="21">
         <f>SUM(CAPEX!B35)</f>
-        <v>8.2095716495249533</v>
+        <v>8.209571649720889</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="21">
         <f>CAPEX!C35</f>
-        <v>11.02717772183105</v>
+        <v>11.02717772209423</v>
       </c>
       <c r="H5" s="26" t="s">
         <v>55</v>
       </c>
       <c r="I5" s="21">
         <f t="shared" si="0"/>
-        <v>8.2095716495249533</v>
+        <v>8.209571649720889</v>
       </c>
       <c r="K5" s="26" t="s">
         <v>55</v>
       </c>
       <c r="L5" s="21">
         <f t="shared" si="1"/>
-        <v>11.02717772183105</v>
+        <v>11.02717772209423</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
@@ -2869,28 +2869,28 @@
       </c>
       <c r="C6" s="21">
         <f>SUM(CAPEX!B36)</f>
-        <v>10.672443144382438</v>
+        <v>10.672443144637155</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>76</v>
       </c>
       <c r="F6" s="21">
         <f>CAPEX!C36</f>
-        <v>14.335331038380366</v>
+        <v>14.335331038722499</v>
       </c>
       <c r="H6" s="26" t="s">
         <v>76</v>
       </c>
       <c r="I6" s="21">
         <f t="shared" si="0"/>
-        <v>10.672443144382438</v>
+        <v>10.672443144637155</v>
       </c>
       <c r="K6" s="26" t="s">
         <v>76</v>
       </c>
       <c r="L6" s="21">
         <f t="shared" si="1"/>
-        <v>14.335331038380366</v>
+        <v>14.335331038722499</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
@@ -2899,28 +2899,28 @@
       </c>
       <c r="C7" s="21">
         <f>SUM(CAPEX!B37)</f>
-        <v>3.5574810481274799</v>
+        <v>3.5574810482123853</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>57</v>
       </c>
       <c r="F7" s="21">
         <f>CAPEX!C37</f>
-        <v>4.7784436794601222</v>
+        <v>4.778443679574166</v>
       </c>
       <c r="H7" s="26" t="s">
         <v>57</v>
       </c>
       <c r="I7" s="21">
         <f t="shared" si="0"/>
-        <v>3.5574810481274799</v>
+        <v>3.5574810482123853</v>
       </c>
       <c r="K7" s="26" t="s">
         <v>57</v>
       </c>
       <c r="L7" s="21">
         <f t="shared" si="1"/>
-        <v>4.7784436794601222</v>
+        <v>4.778443679574166</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
@@ -2929,28 +2929,28 @@
       </c>
       <c r="C8" s="21">
         <f>SUM(CAPEX!B38)</f>
-        <v>49.804734673784729</v>
+        <v>49.804734674973396</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>58</v>
       </c>
       <c r="F8" s="21">
         <f>CAPEX!C38</f>
-        <v>66.898211512441719</v>
+        <v>66.898211514038337</v>
       </c>
       <c r="H8" s="26" t="s">
         <v>58</v>
       </c>
       <c r="I8" s="21">
         <f t="shared" si="0"/>
-        <v>49.804734673784729</v>
+        <v>49.804734674973396</v>
       </c>
       <c r="K8" s="26" t="s">
         <v>58</v>
       </c>
       <c r="L8" s="21">
         <f t="shared" si="1"/>
-        <v>66.898211512441719</v>
+        <v>66.898211514038337</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
@@ -2959,28 +2959,28 @@
       </c>
       <c r="C9" s="21">
         <f>SUM(CAPEX!B39)</f>
-        <v>7.4707102010677087</v>
+        <v>7.4707102012460087</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>61</v>
       </c>
       <c r="F9" s="21">
         <f>CAPEX!C39</f>
-        <v>10.034731726866257</v>
+        <v>10.034731727105751</v>
       </c>
       <c r="H9" s="26" t="s">
         <v>61</v>
       </c>
       <c r="I9" s="21">
         <f t="shared" si="0"/>
-        <v>7.4707102010677087</v>
+        <v>7.4707102012460087</v>
       </c>
       <c r="K9" s="26" t="s">
         <v>61</v>
       </c>
       <c r="L9" s="21">
         <f t="shared" si="1"/>
-        <v>10.034731726866257</v>
+        <v>10.034731727105751</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
@@ -2989,28 +2989,28 @@
       </c>
       <c r="C10" s="21">
         <f>SUM(CAPEX!B40)</f>
-        <v>57.27544487485244</v>
+        <v>57.275444876219403</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>59</v>
       </c>
       <c r="F10" s="21">
         <f>CAPEX!C40</f>
-        <v>76.932943239307974</v>
+        <v>76.932943241144088</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>59</v>
       </c>
       <c r="I10" s="21">
         <f t="shared" si="0"/>
-        <v>57.27544487485244</v>
+        <v>57.275444876219403</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>59</v>
       </c>
       <c r="L10" s="21">
         <f t="shared" si="1"/>
-        <v>76.932943239307974</v>
+        <v>76.932943241144088</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
@@ -3222,28 +3222,28 @@
       </c>
       <c r="C18" s="17">
         <f>SUM(CAPEX!B45)</f>
-        <v>7.3026174923698104</v>
+        <v>7.3026174925440976</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>36</v>
       </c>
       <c r="F18" s="17">
         <f>CAPEX!C45</f>
-        <v>9.8089479403683377</v>
+        <v>9.808947940602442</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>36</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="0"/>
-        <v>7.3026174923698104</v>
+        <v>7.3026174925440976</v>
       </c>
       <c r="K18" s="13" t="s">
         <v>36</v>
       </c>
       <c r="L18" s="17">
         <f t="shared" si="1"/>
-        <v>9.8089479403683377</v>
+        <v>9.808947940602442</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
@@ -3278,28 +3278,28 @@
       </c>
       <c r="C20" s="17">
         <f>OPEX!G12</f>
-        <v>115.72430573879682</v>
+        <v>115.72430575782197</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>88</v>
       </c>
       <c r="F20" s="17">
         <f>OPEX!H12</f>
-        <v>180.76205843505321</v>
+        <v>180.76205846483776</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>88</v>
       </c>
       <c r="I20" s="17">
         <f>OPEX!G13</f>
-        <v>323.96059311359392</v>
+        <v>323.96059316728514</v>
       </c>
       <c r="K20" s="13" t="s">
         <v>88</v>
       </c>
       <c r="L20" s="17">
         <f>OPEX!H13</f>
-        <v>337.37201005200831</v>
+        <v>337.37201010786441</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
@@ -3308,28 +3308,28 @@
       </c>
       <c r="C21" s="17">
         <f>(C18+C19+C20)</f>
-        <v>123.02692323116662</v>
+        <v>123.02692325036607</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>98</v>
       </c>
       <c r="F21" s="17">
         <f>(F18+F19+F20)</f>
-        <v>190.57100637542155</v>
+        <v>190.57100640544022</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>98</v>
       </c>
       <c r="I21" s="17">
         <f>(I18+I19+I20)</f>
-        <v>331.26321060596371</v>
+        <v>331.26321065982921</v>
       </c>
       <c r="K21" s="13" t="s">
         <v>98</v>
       </c>
       <c r="L21" s="17">
         <f>(L18+L19+L20)</f>
-        <v>347.18095799237665</v>
+        <v>347.18095804846683</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
@@ -3338,28 +3338,28 @@
       </c>
       <c r="C22" s="17">
         <f>(C21)*1000000/8000</f>
-        <v>15378.365403895827</v>
+        <v>15378.365406295758</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>97</v>
       </c>
       <c r="F22" s="17">
         <f>(F21)*1000000/8000</f>
-        <v>23821.375796927696</v>
+        <v>23821.375800680027</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>97</v>
       </c>
       <c r="I22" s="17">
         <f>(I21)*1000000/8000</f>
-        <v>41407.901325745464</v>
+        <v>41407.90133247865</v>
       </c>
       <c r="K22" s="13" t="s">
         <v>97</v>
       </c>
       <c r="L22" s="17">
         <f>(L21)*1000000/8000</f>
-        <v>43397.61974904708</v>
+        <v>43397.619756058361</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
@@ -3397,64 +3397,47 @@
       </c>
       <c r="C24" s="45">
         <f>C22/C23</f>
-        <v>0.41008893396804125</v>
+        <v>0.41008893403203933</v>
       </c>
       <c r="E24" s="30" t="s">
         <v>114</v>
       </c>
       <c r="F24" s="45">
         <f>F22/F23</f>
-        <v>0.63523543300248353</v>
+        <v>0.63523543310254549</v>
       </c>
       <c r="H24" s="30" t="s">
         <v>114</v>
       </c>
       <c r="I24" s="45">
         <f>I22/I23</f>
-        <v>1.1042085206420571</v>
+        <v>1.1042085208216084</v>
       </c>
       <c r="K24" s="30" t="s">
         <v>114</v>
       </c>
       <c r="L24" s="45">
         <f>L22/L23</f>
-        <v>1.1572675737779399</v>
+        <v>1.157267573964907</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F26" s="55">
-        <f>OPEX!H6/Summary!F23</f>
-        <v>0.59594290902151548</v>
-      </c>
-      <c r="I26">
-        <f>I18*10^6/8000/I23</f>
-        <v>2.4342010219951988E-2</v>
-      </c>
-      <c r="L26">
-        <f>L18*10^6/8000/L23</f>
-        <v>3.2696428542355264E-2</v>
-      </c>
+      <c r="F26" s="48"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F27" s="55">
-        <f>OPEX!H7/Summary!F23</f>
-        <v>1.1179750497969718</v>
-      </c>
+      <c r="F27" s="48"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F28" s="55">
-        <f>F18*10^6/8000/F23</f>
-        <v>3.2696428542355264E-2</v>
-      </c>
+      <c r="F28" s="48"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F29" s="55"/>
+      <c r="F29" s="48"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F30" s="55"/>
+      <c r="F30" s="48"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F31" s="55"/>
+      <c r="F31" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="4">
